--- a/data/trans_orig/DCD-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2012</t>
+          <t>Población con dolor crónico discapacitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100749</t>
+          <t>100227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144682</t>
+          <t>143780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292174</t>
+          <t>296582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>359098</t>
+          <t>362538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>403662</t>
+          <t>407436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>482635</t>
+          <t>485588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>829961</t>
+          <t>830863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>873894</t>
+          <t>874416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>978699</t>
+          <t>975259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1045623</t>
+          <t>1041215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1829805</t>
+          <t>1826852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1908778</t>
+          <t>1905004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78066</t>
+          <t>79683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117826</t>
+          <t>118707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>184775</t>
+          <t>183916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243163</t>
+          <t>240494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276369</t>
+          <t>273800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>344610</t>
+          <t>345884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1846131</t>
+          <t>1845250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1885891</t>
+          <t>1884274</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1514640</t>
+          <t>1517309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1573028</t>
+          <t>1573887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3377150</t>
+          <t>3375876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3445391</t>
+          <t>3447960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32611</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59836</t>
+          <t>59938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>41834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72634</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461220</t>
+          <t>461034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>475357</t>
+          <t>476009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>398795</t>
+          <t>398693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426020</t>
+          <t>424913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867179</t>
+          <t>866708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>898026</t>
+          <t>897979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198959</t>
+          <t>201634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258314</t>
+          <t>261359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>535781</t>
+          <t>537570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>622143</t>
+          <t>633312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>757468</t>
+          <t>753095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>866106</t>
+          <t>862089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3161468</t>
+          <t>3158423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3220823</t>
+          <t>3218148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2932087</t>
+          <t>2920918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3018449</t>
+          <t>3016660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6107906</t>
+          <t>6111923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6216544</t>
+          <t>6220917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2016</t>
+          <t>Población con dolor crónico discapacitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75199</t>
+          <t>77396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111921</t>
+          <t>112357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185705</t>
+          <t>187451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>239160</t>
+          <t>240437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>273676</t>
+          <t>272117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>339858</t>
+          <t>340967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>642426</t>
+          <t>641990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679148</t>
+          <t>676951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>755500</t>
+          <t>754223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>808955</t>
+          <t>807209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1409149</t>
+          <t>1408040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1475331</t>
+          <t>1476890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88707</t>
+          <t>90628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130765</t>
+          <t>132002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180577</t>
+          <t>181896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237985</t>
+          <t>239564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>284821</t>
+          <t>285165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>357390</t>
+          <t>357054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1945620</t>
+          <t>1944383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1987678</t>
+          <t>1985757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1750315</t>
+          <t>1748736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1807723</t>
+          <t>1806404</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3707295</t>
+          <t>3707631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3779864</t>
+          <t>3779520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37636</t>
+          <t>39085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>49159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82746</t>
+          <t>83060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509250</t>
+          <t>507801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531198</t>
+          <t>530933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496177</t>
+          <t>496813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>521117</t>
+          <t>521556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1013281</t>
+          <t>1012967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1046226</t>
+          <t>1046868</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200819</t>
+          <t>201135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259046</t>
+          <t>262201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>421505</t>
+          <t>420452</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>506472</t>
+          <t>508911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>638517</t>
+          <t>641486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>742131</t>
+          <t>740657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3118572</t>
+          <t>3115417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3176799</t>
+          <t>3176483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3025628</t>
+          <t>3023189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3110595</t>
+          <t>3111648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6167587</t>
+          <t>6169061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6271201</t>
+          <t>6268232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2023</t>
+          <t>Población con dolor crónico discapacitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116207</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150880</t>
+          <t>151889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>309021</t>
+          <t>308849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>351079</t>
+          <t>351349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>434549</t>
+          <t>436153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>491461</t>
+          <t>488337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>364058</t>
+          <t>363049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398731</t>
+          <t>397496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>404429</t>
+          <t>404159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446487</t>
+          <t>446659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>778985</t>
+          <t>782109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>835897</t>
+          <t>834293</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173004</t>
+          <t>164935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>283542</t>
+          <t>278522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>318244</t>
+          <t>331879</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>503224</t>
+          <t>504307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>532178</t>
+          <t>540367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>760919</t>
+          <t>762876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2006785</t>
+          <t>2011805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2117323</t>
+          <t>2125392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1734599</t>
+          <t>1733516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1919579</t>
+          <t>1905944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3767231</t>
+          <t>3765274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3995972</t>
+          <t>3987783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39278</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65368</t>
+          <t>64237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110584</t>
+          <t>112409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147282</t>
+          <t>149440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157763</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201333</t>
+          <t>203577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581255</t>
+          <t>582386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>607345</t>
+          <t>608054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513181</t>
+          <t>511023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>549879</t>
+          <t>548054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1105753</t>
+          <t>1103509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1149323</t>
+          <t>1149061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>334084</t>
+          <t>336878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>475244</t>
+          <t>472634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>712815</t>
+          <t>733465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>974185</t>
+          <t>979327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1158528</t>
+          <t>1147027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1429816</t>
+          <t>1422852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2976645</t>
+          <t>2979255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3117805</t>
+          <t>3115011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2679609</t>
+          <t>2674467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2940979</t>
+          <t>2920329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5675867</t>
+          <t>5682831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5947155</t>
+          <t>5958656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143780</t>
+          <t>144059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>296582</t>
+          <t>295238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>362538</t>
+          <t>356764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>407436</t>
+          <t>405512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>485588</t>
+          <t>481573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>830863</t>
+          <t>830584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>874416</t>
+          <t>874263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>975259</t>
+          <t>981033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1041215</t>
+          <t>1042559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1826852</t>
+          <t>1830867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1905004</t>
+          <t>1906928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79683</t>
+          <t>78700</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118707</t>
+          <t>117091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>183916</t>
+          <t>185022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240494</t>
+          <t>243484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273800</t>
+          <t>274966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>345884</t>
+          <t>343494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1845250</t>
+          <t>1846866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1884274</t>
+          <t>1885257</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1517309</t>
+          <t>1514319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1573887</t>
+          <t>1572781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3375876</t>
+          <t>3378266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3447960</t>
+          <t>3446794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20147</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>31550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59938</t>
+          <t>59081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41834</t>
+          <t>42147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73105</t>
+          <t>74251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461034</t>
+          <t>460871</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476009</t>
+          <t>475267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>398693</t>
+          <t>399550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424913</t>
+          <t>427081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866708</t>
+          <t>865562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>897979</t>
+          <t>897666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201634</t>
+          <t>199805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261359</t>
+          <t>258046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>537570</t>
+          <t>537371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>633312</t>
+          <t>622291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>753095</t>
+          <t>755693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>862089</t>
+          <t>863594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3158423</t>
+          <t>3161736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3218148</t>
+          <t>3219977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2920918</t>
+          <t>2931939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3016660</t>
+          <t>3016859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6111923</t>
+          <t>6110418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6220917</t>
+          <t>6218319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77396</t>
+          <t>75601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112357</t>
+          <t>111256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187451</t>
+          <t>183344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240437</t>
+          <t>241219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272117</t>
+          <t>274345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>340967</t>
+          <t>339605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641990</t>
+          <t>643091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>676951</t>
+          <t>678746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>754223</t>
+          <t>753441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>807209</t>
+          <t>811316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1408040</t>
+          <t>1409402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1476890</t>
+          <t>1474662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90628</t>
+          <t>90746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132002</t>
+          <t>132333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181896</t>
+          <t>182193</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239564</t>
+          <t>242392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>285165</t>
+          <t>284810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>357054</t>
+          <t>355603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1944383</t>
+          <t>1944052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1985757</t>
+          <t>1985639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1748736</t>
+          <t>1745908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1806404</t>
+          <t>1806107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3707631</t>
+          <t>3709082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3779520</t>
+          <t>3779875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>38396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49159</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83060</t>
+          <t>85071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507801</t>
+          <t>508490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530933</t>
+          <t>530733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496813</t>
+          <t>495766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>521556</t>
+          <t>521256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1012967</t>
+          <t>1010956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1046868</t>
+          <t>1045628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201135</t>
+          <t>197851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262201</t>
+          <t>258644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>420452</t>
+          <t>422415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>508911</t>
+          <t>507100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>641486</t>
+          <t>636686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>740657</t>
+          <t>742295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3115417</t>
+          <t>3118974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3176483</t>
+          <t>3179767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3023189</t>
+          <t>3025000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3111648</t>
+          <t>3109685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6169061</t>
+          <t>6167423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6268232</t>
+          <t>6273032</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>133758</t>
+          <t>143299</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117442</t>
+          <t>124631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151889</t>
+          <t>163410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>329675</t>
+          <t>355380</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308849</t>
+          <t>334427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>351349</t>
+          <t>377508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>463433</t>
+          <t>498678</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>436153</t>
+          <t>467741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>488337</t>
+          <t>529152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>381180</t>
+          <t>435230</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363049</t>
+          <t>415119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397496</t>
+          <t>453898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>425833</t>
+          <t>466658</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>404159</t>
+          <t>444530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446659</t>
+          <t>487611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>807013</t>
+          <t>901889</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>782109</t>
+          <t>871415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>834293</t>
+          <t>932826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>238983</t>
+          <t>255304</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164935</t>
+          <t>223827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>278522</t>
+          <t>288388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>439904</t>
+          <t>492761</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>331879</t>
+          <t>459440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>504307</t>
+          <t>531285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>678887</t>
+          <t>748065</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>540367</t>
+          <t>702534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>762876</t>
+          <t>798005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2051344</t>
+          <t>1975262</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2011805</t>
+          <t>1942178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2125392</t>
+          <t>2006739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1797919</t>
+          <t>1678631</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1733516</t>
+          <t>1640107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1905944</t>
+          <t>1711952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3849263</t>
+          <t>3653894</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3765274</t>
+          <t>3603954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3987783</t>
+          <t>3699425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>56308</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>42768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64237</t>
+          <t>71438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>148377</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112409</t>
+          <t>130182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149440</t>
+          <t>169580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>180452</t>
+          <t>204685</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158025</t>
+          <t>180604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203577</t>
+          <t>234695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>595319</t>
+          <t>655279</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>582386</t>
+          <t>640149</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608054</t>
+          <t>668819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>531315</t>
+          <t>586500</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511023</t>
+          <t>565297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548054</t>
+          <t>604695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1126634</t>
+          <t>1241779</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1103509</t>
+          <t>1211769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1149061</t>
+          <t>1265860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>336878</t>
+          <t>414744</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>472634</t>
+          <t>496011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>898727</t>
+          <t>996518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>733465</t>
+          <t>951645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>979327</t>
+          <t>1044161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1322772</t>
+          <t>1451429</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1147027</t>
+          <t>1390575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1422852</t>
+          <t>1514420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3027844</t>
+          <t>3065772</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2979255</t>
+          <t>3024672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3115011</t>
+          <t>3105939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2755067</t>
+          <t>2731789</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2674467</t>
+          <t>2684146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2920329</t>
+          <t>2776662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5782911</t>
+          <t>5797561</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5682831</t>
+          <t>5734570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5958656</t>
+          <t>5858415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
